--- a/part1-portfolio-snapshot/visualizations/portfolio_analysis.xlsx
+++ b/part1-portfolio-snapshot/visualizations/portfolio_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annaw\Desktop\lendinvest-assessment\part1-portfolio-snapshot\visualizations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C3B109-B824-47ED-99D2-18E657A16110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF084D59-6589-4A76-AECB-BDCFA7412C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -658,9 +658,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -679,11 +676,1629 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="297">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -939,6 +2554,12 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -982,9 +2603,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1004,9 +2622,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1026,9 +2641,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1048,9 +2660,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1070,9 +2679,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1092,9 +2698,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1107,43 +2710,25 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
+      <border>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -1153,18 +2738,9 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1175,18 +2751,9 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1197,18 +2764,9 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1219,18 +2777,9 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1241,18 +2790,9 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1263,188 +2803,12 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
@@ -1463,12 +2827,6 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -1485,1364 +2843,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -23874,6 +23874,248 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{02E1A1A0-6249-4A10-B216-CA1B5F6B6CCD}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21" rowHeaderCaption="Region">
+  <location ref="L26:N32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Average percentage repaid" fld="13" subtotal="average" baseField="4" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="18">
+    <format dxfId="23">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="20" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="20" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{215137CC-0BDC-46C7-8767-3429A913848D}" name="PivotTable18" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="21">
   <location ref="R5:U9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
@@ -23939,78 +24181,78 @@
     <dataField name="LTV Band" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="17">
+    <format dxfId="236">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="235">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="234">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="233">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="232">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="14" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="231">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="230">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="229">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="228">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="227">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="226">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="14" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="225">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="224">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="223">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="222">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="221">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="220">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="14" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="219">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
@@ -24104,14 +24346,14 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F884832B-EAEF-4A56-ABB8-7696C7FDB233}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19" rowHeaderCaption="product-type" colHeaderCaption="status">
-  <location ref="B15:E19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7AA3177-EA9D-43FC-B828-BF5DA0CAF9C9}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
+  <location ref="B5:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField name="Product" axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
       <items count="4">
         <item x="2"/>
         <item x="0"/>
@@ -24120,38 +24362,28 @@
       </items>
       <autoSortScope>
         <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="2">
+          <references count="1">
             <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="9" count="1" selected="0">
               <x v="0"/>
             </reference>
           </references>
         </pivotArea>
       </autoSortScope>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
@@ -24160,369 +24392,6 @@
     </i>
     <i>
       <x v="1"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="9"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name=" " fld="7" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="39">
-    <format dxfId="230">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="229">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="228">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="227">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="226">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="225">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="224">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="223">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="222">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="221">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="220">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="219">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="218">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="217">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="216">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="215">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="214">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="213">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="212">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="211">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="210">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="209">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="208">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="207">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="206">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="205">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="204">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="203">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="202">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="201">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="200">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="199">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="198">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="197">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="196">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="195">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="194">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="193">
-      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="192">
-      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="9">
-    <chartFormat chart="4" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="9" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B44A62FF-7CF2-4CA6-B017-2761AB91E4F2}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Region">
-  <location ref="L5:M12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -24534,91 +24403,77 @@
   <dataFields count="1">
     <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
-  <formats count="20">
-    <format dxfId="250">
+  <formats count="19">
+    <format dxfId="255">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="249">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="248">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="247">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="246">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="245">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+    <format dxfId="254">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="4" count="0"/>
+          <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="244">
+    <format dxfId="253">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="243">
+    <format dxfId="252">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="251">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="242">
+    <format dxfId="250">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="241">
+    <format dxfId="249">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="240">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    <format dxfId="248">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="239">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+    <format dxfId="247">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="4" count="0"/>
+          <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="244">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="243">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="242">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="240">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="239">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
     <format dxfId="238">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="237">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="236">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="235">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="234">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="233">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="232">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="231">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
   </formats>
-  <chartFormats count="1">
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -24721,26 +24576,26 @@
     <dataField name="Average of ltv_at_origination" fld="12" subtotal="average" baseField="2" baseItem="3" numFmtId="2"/>
   </dataFields>
   <formats count="20">
-    <format dxfId="270">
+    <format dxfId="275">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="269">
+    <format dxfId="274">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="268">
+    <format dxfId="273">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="267">
+    <format dxfId="272">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="266">
+    <format dxfId="271">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="265">
+    <format dxfId="270">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -24750,26 +24605,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="264">
+    <format dxfId="269">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="263">
+    <format dxfId="268">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="262">
+    <format dxfId="267">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="261">
+    <format dxfId="266">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="260">
+    <format dxfId="265">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="259">
+    <format dxfId="264">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -24779,26 +24634,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="258">
+    <format dxfId="263">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="257">
+    <format dxfId="262">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="256">
+    <format dxfId="261">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="255">
+    <format dxfId="260">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="254">
+    <format dxfId="259">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="253">
+    <format dxfId="258">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -24808,7 +24663,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="252">
+    <format dxfId="257">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -24817,7 +24672,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="251">
+    <format dxfId="256">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -24860,6 +24715,318 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{597AFABC-3AA8-43F1-B90A-DF98CF0209C7}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16" rowHeaderCaption="Broker">
+  <location ref="G26:I31" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="6">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Average percentage repaid" fld="13" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="21">
+    <format dxfId="296">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="295">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="294">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="293">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="292">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="291">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="290">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="289">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="288">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="287">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="286">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="285">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="284">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="283">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="282">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="281">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="280">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="279">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="278">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="277">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="276">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="14">
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ACE8CF37-EF53-4B2A-ACCE-D9AB4D2CA2E3}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Broker">
   <location ref="G5:H11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -24916,76 +25083,76 @@
     <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="20">
-    <format dxfId="290">
+    <format dxfId="43">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="289">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="288">
+    <format dxfId="41">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="287">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="286">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="285">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="284">
+    <format dxfId="37">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="283">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="282">
+    <format dxfId="35">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="281">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="280">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="279">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="278">
+    <format dxfId="31">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="277">
+    <format dxfId="30">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="276">
+    <format dxfId="29">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="275">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="274">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="273">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="272">
+    <format dxfId="25">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="271">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -25012,150 +25179,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7AA3177-EA9D-43FC-B828-BF5DA0CAF9C9}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
-  <location ref="B5:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField name="Product" axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="19">
-    <format dxfId="36">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="30">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="27">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="25">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{02E1A1A0-6249-4A10-B216-CA1B5F6B6CCD}" name="PivotTable14" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21" rowHeaderCaption="Region">
-  <location ref="L26:N32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FA8439D-0566-4FA1-8BBE-C01FE4642DDA}" name="PivotTable6" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="L35:N41" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -25171,15 +25198,16 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -25216,30 +25244,30 @@
     </i>
   </colItems>
   <dataFields count="2">
-    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Average percentage repaid" fld="13" subtotal="average" baseField="4" baseItem="0" numFmtId="10"/>
+    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Average of ltv_at_origination" fld="12" subtotal="average" baseField="4" baseItem="0"/>
   </dataFields>
-  <formats count="18">
-    <format dxfId="54">
+  <formats count="19">
+    <format dxfId="62">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="61">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="60">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -25249,26 +25277,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="56">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="55">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="54">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -25278,26 +25306,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="50">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="49">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="48">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="46">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -25307,9 +25335,19 @@
         </references>
       </pivotArea>
     </format>
+    <format dxfId="44">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
   </formats>
-  <chartFormats count="8">
-    <chartFormat chart="1" format="0" series="1">
+  <chartFormats count="2">
+    <chartFormat chart="4" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -25318,61 +25356,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="20" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="20" format="5" series="1">
+    <chartFormat chart="4" format="5" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -25395,6 +25379,313 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0DD28034-BDF7-4D0A-A6BD-06CA2DEDF729}" name="PivotTable13" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Product">
+  <location ref="B26:D29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Average percentage repaid" fld="13" subtotal="average" baseField="3" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="20">
+    <format dxfId="82">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="81">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="80">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="79">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="78">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="77">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="76">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="75">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="74">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="73">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="72">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="71">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="70">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="69">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="68">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="67">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="66">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="65">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="64">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="63">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="14">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{873909F6-2390-4975-9DE3-7CD417262754}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="36" rowHeaderCaption="Product">
   <location ref="B35:D38" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -25449,26 +25740,26 @@
     <dataField name="Average of ltv_at_origination" fld="12" subtotal="average" baseField="3" baseItem="0"/>
   </dataFields>
   <formats count="19">
-    <format dxfId="73">
+    <format dxfId="101">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="72">
+    <format dxfId="100">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="71">
+    <format dxfId="99">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="70">
+    <format dxfId="98">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="97">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="68">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -25478,26 +25769,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="95">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="66">
+    <format dxfId="94">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="93">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="64">
+    <format dxfId="92">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -25507,26 +25798,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="89">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="88">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="87">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="86">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="84">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -25536,7 +25827,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="83">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -25686,7 +25977,377 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F884832B-EAEF-4A56-ABB8-7696C7FDB233}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19" rowHeaderCaption="product-type" colHeaderCaption="status">
+  <location ref="B15:E19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="9" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="9"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name=" " fld="7" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="39">
+    <format dxfId="140">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="139">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="138">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="137">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="136">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="135">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="134">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="133">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="132">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="131">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="130">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="129">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="128">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="127">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="126">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="125">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="124">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="123">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="122">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="121">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="120">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="119">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="118">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="117">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="116">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="115">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="114">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="113">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="112">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="111">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="110">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="109">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="108">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="107">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="106">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="105">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="104">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="103">
+      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="102">
+      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="9">
+    <chartFormat chart="4" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C26BCC3E-9B9F-4CA5-864F-B3500AAB625D}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Broker">
   <location ref="G15:J21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
@@ -25758,115 +26419,115 @@
     <dataField name=" " fld="7" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="29">
-    <format dxfId="102">
+    <format dxfId="169">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="101">
+    <format dxfId="168">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="100">
+    <format dxfId="167">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="99">
+    <format dxfId="166">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="98">
+    <format dxfId="165">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="97">
+    <format dxfId="164">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="96">
+    <format dxfId="163">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="95">
+    <format dxfId="162">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="94">
+    <format dxfId="161">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="93">
+    <format dxfId="160">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="92">
+    <format dxfId="159">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="91">
+    <format dxfId="158">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="90">
+    <format dxfId="157">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="89">
+    <format dxfId="156">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="155">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="154">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="153">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="85">
+    <format dxfId="152">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="84">
+    <format dxfId="151">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="83">
+    <format dxfId="150">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="149">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="81">
+    <format dxfId="148">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="80">
+    <format dxfId="147">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="146">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="145">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="77">
+    <format dxfId="144">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="76">
+    <format dxfId="143">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="75">
+    <format dxfId="142">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="141">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
@@ -25996,7 +26657,164 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B44A62FF-7CF2-4CA6-B017-2761AB91E4F2}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Region">
+  <location ref="L5:M12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="20">
+    <format dxfId="189">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="188">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="187">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="186">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="185">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="184">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="183">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="182">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="181">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="180">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="179">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="178">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="177">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="176">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="175">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="174">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="173">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="172">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="171">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="170">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C4EDB0D-323A-46C7-AD7B-E3CFAA35B2C2}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19" rowHeaderCaption="Region">
   <location ref="L15:O22" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
@@ -26072,115 +26890,115 @@
     <dataField name=" " fld="7" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="29">
-    <format dxfId="131">
+    <format dxfId="218">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="130">
+    <format dxfId="217">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="129">
+    <format dxfId="216">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="128">
+    <format dxfId="215">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="127">
+    <format dxfId="214">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="126">
+    <format dxfId="213">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="125">
+    <format dxfId="212">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="124">
+    <format dxfId="211">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="123">
+    <format dxfId="210">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="122">
+    <format dxfId="209">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="121">
+    <format dxfId="208">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="120">
+    <format dxfId="207">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="119">
+    <format dxfId="206">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="118">
+    <format dxfId="205">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="117">
+    <format dxfId="204">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="116">
+    <format dxfId="203">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="115">
+    <format dxfId="202">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="114">
+    <format dxfId="201">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="113">
+    <format dxfId="200">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="112">
+    <format dxfId="199">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="111">
+    <format dxfId="198">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="110">
+    <format dxfId="197">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="109">
+    <format dxfId="196">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="108">
+    <format dxfId="195">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="107">
+    <format dxfId="194">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="106">
+    <format dxfId="193">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="105">
+    <format dxfId="192">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="104">
+    <format dxfId="191">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="103">
+    <format dxfId="190">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="0"/>
@@ -26274,824 +27092,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{597AFABC-3AA8-43F1-B90A-DF98CF0209C7}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16" rowHeaderCaption="Broker">
-  <location ref="G26:I31" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="6">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="10" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Average percentage repaid" fld="13" subtotal="average" baseField="0" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <formats count="21">
-    <format dxfId="152">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="151">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="150">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="149">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="148">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="147">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="146">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="145">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="144">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="143">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="142">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="141">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="140">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="139">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="138">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="137">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="136">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="135">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="134">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="133">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="132">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="14">
-    <chartFormat chart="4" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FA8439D-0566-4FA1-8BBE-C01FE4642DDA}" name="PivotTable6" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="L35:N41" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Average of ltv_at_origination" fld="12" subtotal="average" baseField="4" baseItem="0"/>
-  </dataFields>
-  <formats count="19">
-    <format dxfId="171">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="170">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="169">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="168">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="167">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="166">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="165">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="164">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="163">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="162">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="161">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="160">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="159">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="158">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="157">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="156">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="155">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="154">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="153">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="4" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0DD28034-BDF7-4D0A-A6BD-06CA2DEDF729}" name="PivotTable13" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Product">
-  <location ref="B26:D29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="10" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sum of current_balance" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Average percentage repaid" fld="13" subtotal="average" baseField="3" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <formats count="20">
-    <format dxfId="191">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="190">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="189">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="188">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="187">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="186">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="185">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="184">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="183">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="182">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="181">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="180">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="179">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="178">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="177">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="176">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="175">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="174">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="173">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="172">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="14">
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DB1CFC53-C317-4678-A941-C405E15AEA36}" name="Table2" displayName="Table2" ref="A1:O16" totalsRowShown="0">
   <autoFilter ref="A1:O16" xr:uid="{DB1CFC53-C317-4678-A941-C405E15AEA36}"/>
@@ -27101,16 +27101,16 @@
     <tableColumn id="3" xr3:uid="{50DDBB04-8011-47B7-89C0-C940B36F3490}" name="broker_name"/>
     <tableColumn id="4" xr3:uid="{A7F458EA-72E1-4DD0-9AA4-B26A2BAC6F4F}" name="product_type"/>
     <tableColumn id="5" xr3:uid="{BCFE677E-5B68-4F3F-A2AB-FFA2C3FE4D02}" name="region"/>
-    <tableColumn id="6" xr3:uid="{C1476C9D-6D6C-4594-9E51-1070DDD30031}" name="origination_date" dataDxfId="296"/>
-    <tableColumn id="15" xr3:uid="{371A2DBD-E9ED-4FC7-907A-DEDFDBB8B010}" name="original_balance" dataDxfId="295"/>
-    <tableColumn id="9" xr3:uid="{9434B676-11A3-4C96-AD4F-C40949CFE167}" name="current_balance" dataDxfId="294"/>
+    <tableColumn id="6" xr3:uid="{C1476C9D-6D6C-4594-9E51-1070DDD30031}" name="origination_date" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{371A2DBD-E9ED-4FC7-907A-DEDFDBB8B010}" name="original_balance" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{9434B676-11A3-4C96-AD4F-C40949CFE167}" name="current_balance" dataDxfId="3"/>
     <tableColumn id="20" xr3:uid="{780D9B88-6689-4126-9D24-6263D1F8BDDA}" name="interest_rate"/>
     <tableColumn id="10" xr3:uid="{FD7903C6-FCC3-40EF-BDA5-404AC53512BD}" name="status"/>
     <tableColumn id="11" xr3:uid="{7E5F7787-B7B6-4561-9011-049587BF82C2}" name="arrears_days"/>
-    <tableColumn id="12" xr3:uid="{8602D33D-E46D-4DB9-AB28-F04A5F0D3974}" name="property_value" dataDxfId="293"/>
+    <tableColumn id="12" xr3:uid="{8602D33D-E46D-4DB9-AB28-F04A5F0D3974}" name="property_value" dataDxfId="2"/>
     <tableColumn id="13" xr3:uid="{87B745DE-DF0E-4476-B179-DB0A281D10B5}" name="ltv_at_origination"/>
-    <tableColumn id="22" xr3:uid="{27170AF4-E4D5-46BC-AD3F-9FE62BD609B1}" name="percentage_repaid" dataDxfId="292"/>
-    <tableColumn id="7" xr3:uid="{D85D0B8F-71DA-4A32-8338-A9F132453FA6}" name="ltv-band" dataDxfId="291">
+    <tableColumn id="22" xr3:uid="{27170AF4-E4D5-46BC-AD3F-9FE62BD609B1}" name="percentage_repaid" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{D85D0B8F-71DA-4A32-8338-A9F132453FA6}" name="ltv-band" dataDxfId="0">
       <calculatedColumnFormula>IF(Table2[[#This Row],[ltv_at_origination]]&lt;65,"low", IF(Table2[[#This Row],[ltv_at_origination]]&lt;75,"medium","high"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -27634,29 +27634,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="G2" s="46" t="s">
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="G2" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="L2" s="46" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="L2" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="R2" s="42" t="s">
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="R2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
       <c r="U2"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.35">
@@ -27665,16 +27665,16 @@
       <c r="U3"/>
     </row>
     <row r="4" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="44"/>
+      <c r="C4" s="43"/>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="48"/>
+      <c r="H4" s="47"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20"/>
       <c r="K4" s="20"/>
@@ -28581,16 +28581,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="G4:H4"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L14:O14"/>
     <mergeCell ref="R4:U4"/>
@@ -28598,6 +28588,16 @@
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="G25:I25"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="B14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
